--- a/reference_files/2023_deployment_dates.xlsx
+++ b/reference_files/2023_deployment_dates.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Senior Year - College\Research\DataPullCode\PMDataCals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Senior Year - College\Research\CalibrationCodes\Torrias2025Calibration\voz-data-analysis\reference_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71222CEC-0430-445C-B80F-3FEB284B231D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA51D473-A6A2-48E9-B83A-1C85F128B009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DatesAvailable" sheetId="1" r:id="rId1"/>
-    <sheet name="2023_deployment_dates" sheetId="2" r:id="rId2"/>
+    <sheet name="Deployment Dates" sheetId="2" r:id="rId2"/>
     <sheet name="ExtendingCalibrationData" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -301,10 +301,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -6421,7 +6421,7 @@
         <v>36</v>
       </c>
       <c r="H3" s="6">
-        <f ca="1">OFFSET(DatesAvailable!B17,-'2023_deployment_dates'!F3*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!B17,-'Deployment Dates'!F3*0.2,0)</f>
         <v>45104</v>
       </c>
       <c r="I3" s="6">
@@ -6432,7 +6432,7 @@
         <v>45227</v>
       </c>
       <c r="K3" s="6">
-        <f ca="1">OFFSET(DatesAvailable!B122,'2023_deployment_dates'!G3*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!B122,'Deployment Dates'!G3*0.2,0)</f>
         <v>45239</v>
       </c>
       <c r="L3" t="s">
@@ -6532,7 +6532,7 @@
         <v>57</v>
       </c>
       <c r="H5" s="6">
-        <f ca="1">OFFSET(DatesAvailable!D31,-'2023_deployment_dates'!F5*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!D31,-'Deployment Dates'!F5*0.2,0)</f>
         <v>45107</v>
       </c>
       <c r="I5" s="6">
@@ -6542,7 +6542,7 @@
         <v>45233</v>
       </c>
       <c r="K5" s="6">
-        <f ca="1">OFFSET(DatesAvailable!D136,'2023_deployment_dates'!G5*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!D136,'Deployment Dates'!G5*0.2,0)</f>
         <v>45244</v>
       </c>
       <c r="L5" t="s">
@@ -6588,7 +6588,7 @@
         <v>26</v>
       </c>
       <c r="H6" s="6">
-        <f ca="1">OFFSET(DatesAvailable!E24,-'2023_deployment_dates'!F6*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!E24,-'Deployment Dates'!F6*0.2,0)</f>
         <v>45102</v>
       </c>
       <c r="I6" s="6">
@@ -6598,7 +6598,7 @@
         <v>45233</v>
       </c>
       <c r="K6" s="6">
-        <f ca="1">OFFSET(DatesAvailable!E127,'2023_deployment_dates'!G6*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!E127,'Deployment Dates'!G6*0.2,0)</f>
         <v>45247</v>
       </c>
       <c r="L6" t="s">
@@ -6646,7 +6646,7 @@
         <v>45227</v>
       </c>
       <c r="I7" s="6">
-        <f ca="1">OFFSET(DatesAvailable!F99,'2023_deployment_dates'!G7*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!F99,'Deployment Dates'!G7*0.2,0)</f>
         <v>45247</v>
       </c>
       <c r="J7" s="6">
@@ -6700,7 +6700,7 @@
         <v>31</v>
       </c>
       <c r="H8" s="6">
-        <f ca="1">OFFSET(DatesAvailable!G15,-'2023_deployment_dates'!F8*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!G15,-'Deployment Dates'!F8*0.2,0)</f>
         <v>45095</v>
       </c>
       <c r="I8" s="6">
@@ -6710,7 +6710,7 @@
         <v>45227</v>
       </c>
       <c r="K8" s="6">
-        <f ca="1">OFFSET(DatesAvailable!G132,'2023_deployment_dates'!G8*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!G132,'Deployment Dates'!G8*0.2,0)</f>
         <v>45238</v>
       </c>
       <c r="L8" t="s">
@@ -6756,7 +6756,7 @@
         <v>12</v>
       </c>
       <c r="H9" s="6">
-        <f ca="1">OFFSET(DatesAvailable!H16,-'2023_deployment_dates'!F9*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!H16,-'Deployment Dates'!F9*0.2,0)</f>
         <v>45095</v>
       </c>
       <c r="I9" s="6">
@@ -6766,7 +6766,7 @@
         <v>45233</v>
       </c>
       <c r="K9" s="6">
-        <f ca="1">OFFSET(DatesAvailable!H135,'2023_deployment_dates'!G9*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!H135,'Deployment Dates'!G9*0.2,0)</f>
         <v>45246</v>
       </c>
       <c r="L9" t="s">
@@ -6812,7 +6812,7 @@
         <v>30</v>
       </c>
       <c r="H10" s="6">
-        <f ca="1">OFFSET(DatesAvailable!I23,-'2023_deployment_dates'!F10*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!I23,-'Deployment Dates'!F10*0.2,0)</f>
         <v>45101</v>
       </c>
       <c r="I10" s="6">
@@ -6822,7 +6822,7 @@
         <v>45227</v>
       </c>
       <c r="K10" s="6">
-        <f ca="1">OFFSET(DatesAvailable!I112,'2023_deployment_dates'!G10*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!I112,'Deployment Dates'!G10*0.2,0)</f>
         <v>45238</v>
       </c>
       <c r="L10" t="s">
@@ -6868,7 +6868,7 @@
         <v>22</v>
       </c>
       <c r="H11" s="6">
-        <f ca="1">OFFSET(DatesAvailable!J24,-'2023_deployment_dates'!F11*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!J24,-'Deployment Dates'!F11*0.2,0)</f>
         <v>45115</v>
       </c>
       <c r="I11" s="6">
@@ -6878,7 +6878,7 @@
         <v>45244</v>
       </c>
       <c r="K11" s="6">
-        <f ca="1">OFFSET(DatesAvailable!J112,'2023_deployment_dates'!G11*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!J112,'Deployment Dates'!G11*0.2,0)</f>
         <v>45248</v>
       </c>
       <c r="L11" t="s">

--- a/reference_files/2023_deployment_dates.xlsx
+++ b/reference_files/2023_deployment_dates.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Senior Year - College\Research\CalibrationCodes\Torrias2025Calibration\voz-data-analysis\reference_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA51D473-A6A2-48E9-B83A-1C85F128B009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC977ED-A4C3-4A14-9625-ABD61D8BC5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DatesAvailable" sheetId="1" r:id="rId1"/>
-    <sheet name="Deployment Dates" sheetId="2" r:id="rId2"/>
-    <sheet name="ExtendingCalibrationData" sheetId="3" r:id="rId3"/>
+    <sheet name="Both" sheetId="2" r:id="rId2"/>
+    <sheet name="Pre" sheetId="4" r:id="rId3"/>
+    <sheet name="Post" sheetId="5" r:id="rId4"/>
+    <sheet name="ExtendingCalibrationData" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="53">
   <si>
     <t>VOZ_Box_Fresno_mod.csv</t>
   </si>
@@ -6367,7 +6369,8 @@
         <v>57</v>
       </c>
       <c r="H2" s="6">
-        <v>45113</v>
+        <f>C2</f>
+        <v>45099</v>
       </c>
       <c r="I2" s="6">
         <v>45231</v>
@@ -6382,18 +6385,20 @@
         <v>28</v>
       </c>
       <c r="M2" s="6">
+        <f>B2</f>
         <v>45084</v>
       </c>
       <c r="N2" s="6">
         <f>H2</f>
-        <v>45113</v>
+        <v>45099</v>
       </c>
       <c r="O2" s="6">
         <f>K2</f>
         <v>45231</v>
       </c>
       <c r="P2" s="6">
-        <v>45264</v>
+        <f>E2</f>
+        <v>45291</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -6421,7 +6426,7 @@
         <v>36</v>
       </c>
       <c r="H3" s="6">
-        <f ca="1">OFFSET(DatesAvailable!B17,-'Deployment Dates'!F3*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!B17,-Both!F3*0.2,0)</f>
         <v>45104</v>
       </c>
       <c r="I3" s="6">
@@ -6432,7 +6437,7 @@
         <v>45227</v>
       </c>
       <c r="K3" s="6">
-        <f ca="1">OFFSET(DatesAvailable!B122,'Deployment Dates'!G3*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!B122,Both!G3*0.2,0)</f>
         <v>45239</v>
       </c>
       <c r="L3" t="s">
@@ -6450,7 +6455,7 @@
         <v>45239</v>
       </c>
       <c r="P3" s="6">
-        <v>45270</v>
+        <v>45249</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -6478,16 +6483,20 @@
         <v>33</v>
       </c>
       <c r="H4" s="6">
-        <v>45140</v>
+        <f>DatesAvailable!C19</f>
+        <v>45109</v>
       </c>
       <c r="I4" s="6">
+        <f>H4+5</f>
+        <v>45114</v>
+      </c>
+      <c r="J4" s="6">
+        <f>DatesAvailable!C124</f>
         <v>45233</v>
       </c>
-      <c r="J4" s="6">
-        <v>45233</v>
-      </c>
       <c r="K4" s="6">
-        <v>45233</v>
+        <f>DatesAvailable!C129</f>
+        <v>45238</v>
       </c>
       <c r="L4" t="s">
         <v>28</v>
@@ -6497,14 +6506,15 @@
       </c>
       <c r="N4" s="6">
         <f t="shared" si="0"/>
-        <v>45140</v>
+        <v>45109</v>
       </c>
       <c r="O4" s="6">
         <f t="shared" si="1"/>
-        <v>45233</v>
+        <v>45238</v>
       </c>
       <c r="P4" s="6">
-        <v>45280</v>
+        <f>DatesAvailable!C146</f>
+        <v>45269</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -6532,7 +6542,7 @@
         <v>57</v>
       </c>
       <c r="H5" s="6">
-        <f ca="1">OFFSET(DatesAvailable!D31,-'Deployment Dates'!F5*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!D31,-Both!F5*0.2,0)</f>
         <v>45107</v>
       </c>
       <c r="I5" s="6">
@@ -6542,7 +6552,7 @@
         <v>45233</v>
       </c>
       <c r="K5" s="6">
-        <f ca="1">OFFSET(DatesAvailable!D136,'Deployment Dates'!G5*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!D136,Both!G5*0.2,0)</f>
         <v>45244</v>
       </c>
       <c r="L5" t="s">
@@ -6588,7 +6598,7 @@
         <v>26</v>
       </c>
       <c r="H6" s="6">
-        <f ca="1">OFFSET(DatesAvailable!E24,-'Deployment Dates'!F6*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!E24,-Both!F6*0.2,0)</f>
         <v>45102</v>
       </c>
       <c r="I6" s="6">
@@ -6598,7 +6608,7 @@
         <v>45233</v>
       </c>
       <c r="K6" s="6">
-        <f ca="1">OFFSET(DatesAvailable!E127,'Deployment Dates'!G6*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!E127,Both!G6*0.2,0)</f>
         <v>45247</v>
       </c>
       <c r="L6" t="s">
@@ -6646,7 +6656,7 @@
         <v>45227</v>
       </c>
       <c r="I7" s="6">
-        <f ca="1">OFFSET(DatesAvailable!F99,'Deployment Dates'!G7*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!F99,Both!G7*0.2,0)</f>
         <v>45247</v>
       </c>
       <c r="J7" s="6">
@@ -6700,7 +6710,7 @@
         <v>31</v>
       </c>
       <c r="H8" s="6">
-        <f ca="1">OFFSET(DatesAvailable!G15,-'Deployment Dates'!F8*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!G15,-Both!F8*0.2,0)</f>
         <v>45095</v>
       </c>
       <c r="I8" s="6">
@@ -6710,7 +6720,7 @@
         <v>45227</v>
       </c>
       <c r="K8" s="6">
-        <f ca="1">OFFSET(DatesAvailable!G132,'Deployment Dates'!G8*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!G132,Both!G8*0.2,0)</f>
         <v>45238</v>
       </c>
       <c r="L8" t="s">
@@ -6756,7 +6766,7 @@
         <v>12</v>
       </c>
       <c r="H9" s="6">
-        <f ca="1">OFFSET(DatesAvailable!H16,-'Deployment Dates'!F9*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!H16,-Both!F9*0.2,0)</f>
         <v>45095</v>
       </c>
       <c r="I9" s="6">
@@ -6766,7 +6776,7 @@
         <v>45233</v>
       </c>
       <c r="K9" s="6">
-        <f ca="1">OFFSET(DatesAvailable!H135,'Deployment Dates'!G9*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!H135,Both!G9*0.2,0)</f>
         <v>45246</v>
       </c>
       <c r="L9" t="s">
@@ -6812,7 +6822,7 @@
         <v>30</v>
       </c>
       <c r="H10" s="6">
-        <f ca="1">OFFSET(DatesAvailable!I23,-'Deployment Dates'!F10*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!I23,-Both!F10*0.2,0)</f>
         <v>45101</v>
       </c>
       <c r="I10" s="6">
@@ -6822,7 +6832,7 @@
         <v>45227</v>
       </c>
       <c r="K10" s="6">
-        <f ca="1">OFFSET(DatesAvailable!I112,'Deployment Dates'!G10*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!I112,Both!G10*0.2,0)</f>
         <v>45238</v>
       </c>
       <c r="L10" t="s">
@@ -6868,7 +6878,7 @@
         <v>22</v>
       </c>
       <c r="H11" s="6">
-        <f ca="1">OFFSET(DatesAvailable!J24,-'Deployment Dates'!F11*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!J24,-Both!F11*0.2,0)</f>
         <v>45115</v>
       </c>
       <c r="I11" s="6">
@@ -6878,7 +6888,7 @@
         <v>45244</v>
       </c>
       <c r="K11" s="6">
-        <f ca="1">OFFSET(DatesAvailable!J112,'Deployment Dates'!G11*0.2,0)</f>
+        <f ca="1">OFFSET(DatesAvailable!J112,Both!G11*0.2,0)</f>
         <v>45248</v>
       </c>
       <c r="L11" t="s">
@@ -6924,7 +6934,7 @@
         <v>57</v>
       </c>
       <c r="H12" s="6">
-        <v>45098</v>
+        <v>45099</v>
       </c>
       <c r="I12" s="6">
         <v>45231</v>
@@ -6939,17 +6949,18 @@
         <v>28</v>
       </c>
       <c r="M12" s="6">
+        <f>B12</f>
         <v>45084</v>
       </c>
       <c r="N12" s="6">
-        <f t="shared" si="0"/>
-        <v>45098</v>
+        <v>45099</v>
       </c>
       <c r="O12" s="6">
         <f t="shared" si="1"/>
         <v>45231</v>
       </c>
       <c r="P12" s="6">
+        <f>E12</f>
         <v>45291</v>
       </c>
     </row>
@@ -6959,6 +6970,1409 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93424DF1-2AAF-4BF8-830D-D7CB8EA3D9A4}">
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C2" s="6">
+        <v>45099</v>
+      </c>
+      <c r="D2" s="6">
+        <v>45231</v>
+      </c>
+      <c r="E2" s="6">
+        <v>45291</v>
+      </c>
+      <c r="F2">
+        <f>COUNT(DatesAvailable!A2:A17)</f>
+        <v>16</v>
+      </c>
+      <c r="G2">
+        <f>COUNT(DatesAvailable!A137:A193)</f>
+        <v>57</v>
+      </c>
+      <c r="H2" s="6">
+        <f>C2</f>
+        <v>45099</v>
+      </c>
+      <c r="I2" s="6">
+        <v>45231</v>
+      </c>
+      <c r="J2" s="6">
+        <v>45231</v>
+      </c>
+      <c r="K2" s="6">
+        <v>45231</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="6">
+        <f>B2</f>
+        <v>45084</v>
+      </c>
+      <c r="N2" s="6">
+        <f>H2</f>
+        <v>45099</v>
+      </c>
+      <c r="O2" s="6">
+        <f>K2</f>
+        <v>45231</v>
+      </c>
+      <c r="P2" s="6">
+        <f>O2</f>
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="6">
+        <v>45092</v>
+      </c>
+      <c r="C3" s="6">
+        <v>45110</v>
+      </c>
+      <c r="D3" s="6">
+        <v>45227</v>
+      </c>
+      <c r="E3" s="6">
+        <v>45269</v>
+      </c>
+      <c r="F3">
+        <f>COUNT(DatesAvailable!B2:B17)</f>
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <f>COUNT(DatesAvailable!B122:B157)</f>
+        <v>36</v>
+      </c>
+      <c r="H3" s="6">
+        <f ca="1">OFFSET(DatesAvailable!B17,-Both!F3*0.2,0)</f>
+        <v>45104</v>
+      </c>
+      <c r="I3" s="6">
+        <f>C3</f>
+        <v>45110</v>
+      </c>
+      <c r="J3" s="6">
+        <v>45227</v>
+      </c>
+      <c r="K3" s="6">
+        <f ca="1">OFFSET(DatesAvailable!B122,Both!G3*0.2,0)</f>
+        <v>45239</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="6">
+        <v>45092</v>
+      </c>
+      <c r="N3" s="6">
+        <f t="shared" ref="N3:N12" ca="1" si="0">H3</f>
+        <v>45104</v>
+      </c>
+      <c r="O3" s="6">
+        <f t="shared" ref="O3:O12" ca="1" si="1">K3</f>
+        <v>45239</v>
+      </c>
+      <c r="P3" s="6">
+        <f t="shared" ref="P3:P11" ca="1" si="2">O3</f>
+        <v>45239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6">
+        <v>45092</v>
+      </c>
+      <c r="C4" s="6">
+        <v>45140</v>
+      </c>
+      <c r="D4" s="6">
+        <v>45233</v>
+      </c>
+      <c r="E4" s="6">
+        <v>45279</v>
+      </c>
+      <c r="F4">
+        <f>COUNT(DatesAvailable!C2:C23)</f>
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <f>COUNT(DatesAvailable!C124:C156)</f>
+        <v>33</v>
+      </c>
+      <c r="H4" s="6">
+        <f>DatesAvailable!C19</f>
+        <v>45109</v>
+      </c>
+      <c r="I4" s="6">
+        <f>H4+5</f>
+        <v>45114</v>
+      </c>
+      <c r="J4" s="6">
+        <f>DatesAvailable!C124</f>
+        <v>45233</v>
+      </c>
+      <c r="K4" s="6">
+        <f>DatesAvailable!C129</f>
+        <v>45238</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="6">
+        <v>45092</v>
+      </c>
+      <c r="N4" s="6">
+        <f t="shared" si="0"/>
+        <v>45109</v>
+      </c>
+      <c r="O4" s="6">
+        <f t="shared" si="1"/>
+        <v>45238</v>
+      </c>
+      <c r="P4" s="6">
+        <f t="shared" si="2"/>
+        <v>45238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C5" s="6">
+        <v>45114</v>
+      </c>
+      <c r="D5" s="6">
+        <v>45233</v>
+      </c>
+      <c r="E5" s="6">
+        <v>45291</v>
+      </c>
+      <c r="F5">
+        <f>COUNT(DatesAvailable!D2:D31)</f>
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <f>COUNT(DatesAvailable!D136:D192)</f>
+        <v>57</v>
+      </c>
+      <c r="H5" s="6">
+        <f ca="1">OFFSET(DatesAvailable!D31,-Both!F5*0.2,0)</f>
+        <v>45107</v>
+      </c>
+      <c r="I5" s="6">
+        <v>45114</v>
+      </c>
+      <c r="J5" s="6">
+        <v>45233</v>
+      </c>
+      <c r="K5" s="6">
+        <f ca="1">OFFSET(DatesAvailable!D136,Both!G5*0.2,0)</f>
+        <v>45244</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="6">
+        <v>45084</v>
+      </c>
+      <c r="N5" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45107</v>
+      </c>
+      <c r="O5" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45244</v>
+      </c>
+      <c r="P5" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C6" s="6">
+        <v>45118</v>
+      </c>
+      <c r="D6" s="6">
+        <v>45233</v>
+      </c>
+      <c r="E6" s="6">
+        <v>45291</v>
+      </c>
+      <c r="F6">
+        <f>COUNT(DatesAvailable!E2:E24)</f>
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <f>COUNT(DatesAvailable!E127:E152)</f>
+        <v>26</v>
+      </c>
+      <c r="H6" s="6">
+        <f ca="1">OFFSET(DatesAvailable!E24,-Both!F6*0.2,0)</f>
+        <v>45102</v>
+      </c>
+      <c r="I6" s="6">
+        <v>45118</v>
+      </c>
+      <c r="J6" s="6">
+        <v>45233</v>
+      </c>
+      <c r="K6" s="6">
+        <f ca="1">OFFSET(DatesAvailable!E127,Both!G6*0.2,0)</f>
+        <v>45247</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="6">
+        <v>45084</v>
+      </c>
+      <c r="N6" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45102</v>
+      </c>
+      <c r="O6" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45247</v>
+      </c>
+      <c r="P6" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="6">
+        <v>45129</v>
+      </c>
+      <c r="C7" s="6">
+        <v>45129</v>
+      </c>
+      <c r="D7" s="6">
+        <v>45227</v>
+      </c>
+      <c r="E7" s="6">
+        <v>45280</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f>COUNT(DatesAvailable!F99:F121)</f>
+        <v>23</v>
+      </c>
+      <c r="H7" s="6">
+        <v>45227</v>
+      </c>
+      <c r="I7" s="6">
+        <f ca="1">OFFSET(DatesAvailable!F99,Both!G7*0.2,0)</f>
+        <v>45247</v>
+      </c>
+      <c r="J7" s="6">
+        <f ca="1">I7</f>
+        <v>45247</v>
+      </c>
+      <c r="K7" s="6">
+        <f ca="1">J7</f>
+        <v>45247</v>
+      </c>
+      <c r="L7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="6">
+        <v>45129</v>
+      </c>
+      <c r="N7" s="6">
+        <f>M7</f>
+        <v>45129</v>
+      </c>
+      <c r="O7" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45247</v>
+      </c>
+      <c r="P7" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C8" s="6">
+        <v>45098</v>
+      </c>
+      <c r="D8" s="6">
+        <v>45227</v>
+      </c>
+      <c r="E8" s="6">
+        <v>45279</v>
+      </c>
+      <c r="F8">
+        <f>COUNT(DatesAvailable!G2:G15)</f>
+        <v>14</v>
+      </c>
+      <c r="G8">
+        <f>COUNT(DatesAvailable!G132:G162)</f>
+        <v>31</v>
+      </c>
+      <c r="H8" s="6">
+        <f ca="1">OFFSET(DatesAvailable!G15,-Both!F8*0.2,0)</f>
+        <v>45095</v>
+      </c>
+      <c r="I8" s="6">
+        <v>45098</v>
+      </c>
+      <c r="J8" s="6">
+        <v>45227</v>
+      </c>
+      <c r="K8" s="6">
+        <f ca="1">OFFSET(DatesAvailable!G132,Both!G8*0.2,0)</f>
+        <v>45238</v>
+      </c>
+      <c r="L8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="6">
+        <v>45084</v>
+      </c>
+      <c r="N8" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45095</v>
+      </c>
+      <c r="O8" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45238</v>
+      </c>
+      <c r="P8" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C9" s="6">
+        <v>45100</v>
+      </c>
+      <c r="D9" s="6">
+        <v>45233</v>
+      </c>
+      <c r="E9" s="6">
+        <v>45269</v>
+      </c>
+      <c r="F9">
+        <f>COUNT(DatesAvailable!H2:H16)</f>
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <f>COUNT(DatesAvailable!H135:H146)</f>
+        <v>12</v>
+      </c>
+      <c r="H9" s="6">
+        <f ca="1">OFFSET(DatesAvailable!H16,-Both!F9*0.2,0)</f>
+        <v>45095</v>
+      </c>
+      <c r="I9" s="6">
+        <v>45100</v>
+      </c>
+      <c r="J9" s="6">
+        <v>45233</v>
+      </c>
+      <c r="K9" s="6">
+        <f ca="1">OFFSET(DatesAvailable!H135,Both!G9*0.2,0)</f>
+        <v>45246</v>
+      </c>
+      <c r="L9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="6">
+        <v>45084</v>
+      </c>
+      <c r="N9" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45095</v>
+      </c>
+      <c r="O9" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45246</v>
+      </c>
+      <c r="P9" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45246</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C10" s="6">
+        <v>45106</v>
+      </c>
+      <c r="D10" s="6">
+        <v>45227</v>
+      </c>
+      <c r="E10" s="6">
+        <v>45291</v>
+      </c>
+      <c r="F10">
+        <f>COUNT(DatesAvailable!I2:I23)</f>
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <f>COUNT(DatesAvailable!I112:I141)</f>
+        <v>30</v>
+      </c>
+      <c r="H10" s="6">
+        <f ca="1">OFFSET(DatesAvailable!I23,-Both!F10*0.2,0)</f>
+        <v>45101</v>
+      </c>
+      <c r="I10" s="6">
+        <v>45106</v>
+      </c>
+      <c r="J10" s="6">
+        <v>45227</v>
+      </c>
+      <c r="K10" s="6">
+        <f ca="1">OFFSET(DatesAvailable!I112,Both!G10*0.2,0)</f>
+        <v>45238</v>
+      </c>
+      <c r="L10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" s="6">
+        <v>45084</v>
+      </c>
+      <c r="N10" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45101</v>
+      </c>
+      <c r="O10" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45238</v>
+      </c>
+      <c r="P10" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45238</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C11" s="6">
+        <v>45150</v>
+      </c>
+      <c r="D11" s="6">
+        <v>45244</v>
+      </c>
+      <c r="E11" s="6">
+        <v>45279</v>
+      </c>
+      <c r="F11">
+        <f>COUNT(DatesAvailable!J2:J24)</f>
+        <v>23</v>
+      </c>
+      <c r="G11">
+        <f>COUNT(DatesAvailable!J112:J133)</f>
+        <v>22</v>
+      </c>
+      <c r="H11" s="6">
+        <f ca="1">OFFSET(DatesAvailable!J24,-Both!F11*0.2,0)</f>
+        <v>45115</v>
+      </c>
+      <c r="I11" s="6">
+        <v>45150</v>
+      </c>
+      <c r="J11" s="6">
+        <v>45244</v>
+      </c>
+      <c r="K11" s="6">
+        <f ca="1">OFFSET(DatesAvailable!J112,Both!G11*0.2,0)</f>
+        <v>45248</v>
+      </c>
+      <c r="L11" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" s="6">
+        <v>45084</v>
+      </c>
+      <c r="N11" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45115</v>
+      </c>
+      <c r="O11" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45248</v>
+      </c>
+      <c r="P11" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C12" s="6">
+        <v>45098</v>
+      </c>
+      <c r="D12" s="6">
+        <v>45231</v>
+      </c>
+      <c r="E12" s="6">
+        <v>45291</v>
+      </c>
+      <c r="F12">
+        <f>COUNT(DatesAvailable!K2:K16)</f>
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <f>COUNT(DatesAvailable!K137:K193)</f>
+        <v>57</v>
+      </c>
+      <c r="H12" s="6">
+        <v>45099</v>
+      </c>
+      <c r="I12" s="6">
+        <v>45231</v>
+      </c>
+      <c r="J12" s="6">
+        <v>45231</v>
+      </c>
+      <c r="K12" s="6">
+        <v>45231</v>
+      </c>
+      <c r="L12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="6">
+        <f>B12</f>
+        <v>45084</v>
+      </c>
+      <c r="N12" s="6">
+        <v>45099</v>
+      </c>
+      <c r="O12" s="6">
+        <f t="shared" si="1"/>
+        <v>45231</v>
+      </c>
+      <c r="P12" s="6">
+        <f>O12</f>
+        <v>45231</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90088390-3F66-4B47-9086-5BD00CA04B78}">
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C2" s="6">
+        <v>45099</v>
+      </c>
+      <c r="D2" s="6">
+        <v>45231</v>
+      </c>
+      <c r="E2" s="6">
+        <v>45291</v>
+      </c>
+      <c r="F2">
+        <f>COUNT(DatesAvailable!A2:A17)</f>
+        <v>16</v>
+      </c>
+      <c r="G2">
+        <f>COUNT(DatesAvailable!A137:A193)</f>
+        <v>57</v>
+      </c>
+      <c r="H2" s="6">
+        <f>C2</f>
+        <v>45099</v>
+      </c>
+      <c r="I2" s="6">
+        <v>45231</v>
+      </c>
+      <c r="J2" s="6">
+        <v>45231</v>
+      </c>
+      <c r="K2" s="6">
+        <v>45231</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="6">
+        <f>N2</f>
+        <v>45099</v>
+      </c>
+      <c r="N2" s="6">
+        <f>H2</f>
+        <v>45099</v>
+      </c>
+      <c r="O2" s="6">
+        <f>K2</f>
+        <v>45231</v>
+      </c>
+      <c r="P2" s="6">
+        <f>E2</f>
+        <v>45291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="6">
+        <v>45092</v>
+      </c>
+      <c r="C3" s="6">
+        <v>45110</v>
+      </c>
+      <c r="D3" s="6">
+        <v>45227</v>
+      </c>
+      <c r="E3" s="6">
+        <v>45269</v>
+      </c>
+      <c r="F3">
+        <f>COUNT(DatesAvailable!B2:B17)</f>
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <f>COUNT(DatesAvailable!B122:B157)</f>
+        <v>36</v>
+      </c>
+      <c r="H3" s="6">
+        <f ca="1">OFFSET(DatesAvailable!B17,-Both!F3*0.2,0)</f>
+        <v>45104</v>
+      </c>
+      <c r="I3" s="6">
+        <f>C3</f>
+        <v>45110</v>
+      </c>
+      <c r="J3" s="6">
+        <v>45227</v>
+      </c>
+      <c r="K3" s="6">
+        <f ca="1">OFFSET(DatesAvailable!B122,Both!G3*0.2,0)</f>
+        <v>45239</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="6">
+        <f t="shared" ref="M3:M12" ca="1" si="0">N3</f>
+        <v>45104</v>
+      </c>
+      <c r="N3" s="6">
+        <f t="shared" ref="N3:N12" ca="1" si="1">H3</f>
+        <v>45104</v>
+      </c>
+      <c r="O3" s="6">
+        <f t="shared" ref="O3:O12" ca="1" si="2">K3</f>
+        <v>45239</v>
+      </c>
+      <c r="P3" s="6">
+        <v>45249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6">
+        <v>45092</v>
+      </c>
+      <c r="C4" s="6">
+        <v>45140</v>
+      </c>
+      <c r="D4" s="6">
+        <v>45233</v>
+      </c>
+      <c r="E4" s="6">
+        <v>45279</v>
+      </c>
+      <c r="F4">
+        <f>COUNT(DatesAvailable!C2:C23)</f>
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <f>COUNT(DatesAvailable!C124:C156)</f>
+        <v>33</v>
+      </c>
+      <c r="H4" s="6">
+        <f>DatesAvailable!C19</f>
+        <v>45109</v>
+      </c>
+      <c r="I4" s="6">
+        <f>H4+5</f>
+        <v>45114</v>
+      </c>
+      <c r="J4" s="6">
+        <f>DatesAvailable!C124</f>
+        <v>45233</v>
+      </c>
+      <c r="K4" s="6">
+        <f>DatesAvailable!C129</f>
+        <v>45238</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="6">
+        <f t="shared" si="0"/>
+        <v>45109</v>
+      </c>
+      <c r="N4" s="6">
+        <f t="shared" si="1"/>
+        <v>45109</v>
+      </c>
+      <c r="O4" s="6">
+        <f t="shared" si="2"/>
+        <v>45238</v>
+      </c>
+      <c r="P4" s="6">
+        <f>DatesAvailable!C146</f>
+        <v>45269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C5" s="6">
+        <v>45114</v>
+      </c>
+      <c r="D5" s="6">
+        <v>45233</v>
+      </c>
+      <c r="E5" s="6">
+        <v>45291</v>
+      </c>
+      <c r="F5">
+        <f>COUNT(DatesAvailable!D2:D31)</f>
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <f>COUNT(DatesAvailable!D136:D192)</f>
+        <v>57</v>
+      </c>
+      <c r="H5" s="6">
+        <f ca="1">OFFSET(DatesAvailable!D31,-Both!F5*0.2,0)</f>
+        <v>45107</v>
+      </c>
+      <c r="I5" s="6">
+        <v>45114</v>
+      </c>
+      <c r="J5" s="6">
+        <v>45233</v>
+      </c>
+      <c r="K5" s="6">
+        <f ca="1">OFFSET(DatesAvailable!D136,Both!G5*0.2,0)</f>
+        <v>45244</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45107</v>
+      </c>
+      <c r="N5" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45107</v>
+      </c>
+      <c r="O5" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45244</v>
+      </c>
+      <c r="P5" s="6">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C6" s="6">
+        <v>45118</v>
+      </c>
+      <c r="D6" s="6">
+        <v>45233</v>
+      </c>
+      <c r="E6" s="6">
+        <v>45291</v>
+      </c>
+      <c r="F6">
+        <f>COUNT(DatesAvailable!E2:E24)</f>
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <f>COUNT(DatesAvailable!E127:E152)</f>
+        <v>26</v>
+      </c>
+      <c r="H6" s="6">
+        <f ca="1">OFFSET(DatesAvailable!E24,-Both!F6*0.2,0)</f>
+        <v>45102</v>
+      </c>
+      <c r="I6" s="6">
+        <v>45118</v>
+      </c>
+      <c r="J6" s="6">
+        <v>45233</v>
+      </c>
+      <c r="K6" s="6">
+        <f ca="1">OFFSET(DatesAvailable!E127,Both!G6*0.2,0)</f>
+        <v>45247</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45102</v>
+      </c>
+      <c r="N6" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45102</v>
+      </c>
+      <c r="O6" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45247</v>
+      </c>
+      <c r="P6" s="6">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="6">
+        <v>45129</v>
+      </c>
+      <c r="C7" s="6">
+        <v>45129</v>
+      </c>
+      <c r="D7" s="6">
+        <v>45227</v>
+      </c>
+      <c r="E7" s="6">
+        <v>45280</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f>COUNT(DatesAvailable!F99:F121)</f>
+        <v>23</v>
+      </c>
+      <c r="H7" s="6">
+        <v>45227</v>
+      </c>
+      <c r="I7" s="6">
+        <f ca="1">OFFSET(DatesAvailable!F99,Both!G7*0.2,0)</f>
+        <v>45247</v>
+      </c>
+      <c r="J7" s="6">
+        <f ca="1">I7</f>
+        <v>45247</v>
+      </c>
+      <c r="K7" s="6">
+        <f ca="1">J7</f>
+        <v>45247</v>
+      </c>
+      <c r="L7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="6">
+        <f t="shared" si="0"/>
+        <v>45129</v>
+      </c>
+      <c r="N7" s="6">
+        <f>C7</f>
+        <v>45129</v>
+      </c>
+      <c r="O7" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45247</v>
+      </c>
+      <c r="P7" s="6">
+        <v>45281</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C8" s="6">
+        <v>45098</v>
+      </c>
+      <c r="D8" s="6">
+        <v>45227</v>
+      </c>
+      <c r="E8" s="6">
+        <v>45279</v>
+      </c>
+      <c r="F8">
+        <f>COUNT(DatesAvailable!G2:G15)</f>
+        <v>14</v>
+      </c>
+      <c r="G8">
+        <f>COUNT(DatesAvailable!G132:G162)</f>
+        <v>31</v>
+      </c>
+      <c r="H8" s="6">
+        <f ca="1">OFFSET(DatesAvailable!G15,-Both!F8*0.2,0)</f>
+        <v>45095</v>
+      </c>
+      <c r="I8" s="6">
+        <v>45098</v>
+      </c>
+      <c r="J8" s="6">
+        <v>45227</v>
+      </c>
+      <c r="K8" s="6">
+        <f ca="1">OFFSET(DatesAvailable!G132,Both!G8*0.2,0)</f>
+        <v>45238</v>
+      </c>
+      <c r="L8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45095</v>
+      </c>
+      <c r="N8" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45095</v>
+      </c>
+      <c r="O8" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45238</v>
+      </c>
+      <c r="P8" s="6">
+        <v>45280</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C9" s="6">
+        <v>45100</v>
+      </c>
+      <c r="D9" s="6">
+        <v>45233</v>
+      </c>
+      <c r="E9" s="6">
+        <v>45269</v>
+      </c>
+      <c r="F9">
+        <f>COUNT(DatesAvailable!H2:H16)</f>
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <f>COUNT(DatesAvailable!H135:H146)</f>
+        <v>12</v>
+      </c>
+      <c r="H9" s="6">
+        <f ca="1">OFFSET(DatesAvailable!H16,-Both!F9*0.2,0)</f>
+        <v>45095</v>
+      </c>
+      <c r="I9" s="6">
+        <v>45100</v>
+      </c>
+      <c r="J9" s="6">
+        <v>45233</v>
+      </c>
+      <c r="K9" s="6">
+        <f ca="1">OFFSET(DatesAvailable!H135,Both!G9*0.2,0)</f>
+        <v>45246</v>
+      </c>
+      <c r="L9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45095</v>
+      </c>
+      <c r="N9" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45095</v>
+      </c>
+      <c r="O9" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45246</v>
+      </c>
+      <c r="P9" s="6">
+        <v>45270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C10" s="6">
+        <v>45106</v>
+      </c>
+      <c r="D10" s="6">
+        <v>45227</v>
+      </c>
+      <c r="E10" s="6">
+        <v>45291</v>
+      </c>
+      <c r="F10">
+        <f>COUNT(DatesAvailable!I2:I23)</f>
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <f>COUNT(DatesAvailable!I112:I141)</f>
+        <v>30</v>
+      </c>
+      <c r="H10" s="6">
+        <f ca="1">OFFSET(DatesAvailable!I23,-Both!F10*0.2,0)</f>
+        <v>45101</v>
+      </c>
+      <c r="I10" s="6">
+        <v>45106</v>
+      </c>
+      <c r="J10" s="6">
+        <v>45227</v>
+      </c>
+      <c r="K10" s="6">
+        <f ca="1">OFFSET(DatesAvailable!I112,Both!G10*0.2,0)</f>
+        <v>45238</v>
+      </c>
+      <c r="L10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45101</v>
+      </c>
+      <c r="N10" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45101</v>
+      </c>
+      <c r="O10" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45238</v>
+      </c>
+      <c r="P10" s="6">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C11" s="6">
+        <v>45150</v>
+      </c>
+      <c r="D11" s="6">
+        <v>45244</v>
+      </c>
+      <c r="E11" s="6">
+        <v>45279</v>
+      </c>
+      <c r="F11">
+        <f>COUNT(DatesAvailable!J2:J24)</f>
+        <v>23</v>
+      </c>
+      <c r="G11">
+        <f>COUNT(DatesAvailable!J112:J133)</f>
+        <v>22</v>
+      </c>
+      <c r="H11" s="6">
+        <f ca="1">OFFSET(DatesAvailable!J24,-Both!F11*0.2,0)</f>
+        <v>45115</v>
+      </c>
+      <c r="I11" s="6">
+        <v>45150</v>
+      </c>
+      <c r="J11" s="6">
+        <v>45244</v>
+      </c>
+      <c r="K11" s="6">
+        <f ca="1">OFFSET(DatesAvailable!J112,Both!G11*0.2,0)</f>
+        <v>45248</v>
+      </c>
+      <c r="L11" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45115</v>
+      </c>
+      <c r="N11" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45115</v>
+      </c>
+      <c r="O11" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45248</v>
+      </c>
+      <c r="P11" s="6">
+        <v>45280</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6">
+        <v>45084</v>
+      </c>
+      <c r="C12" s="6">
+        <v>45098</v>
+      </c>
+      <c r="D12" s="6">
+        <v>45231</v>
+      </c>
+      <c r="E12" s="6">
+        <v>45291</v>
+      </c>
+      <c r="F12">
+        <f>COUNT(DatesAvailable!K2:K16)</f>
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <f>COUNT(DatesAvailable!K137:K193)</f>
+        <v>57</v>
+      </c>
+      <c r="H12" s="6">
+        <v>45099</v>
+      </c>
+      <c r="I12" s="6">
+        <v>45231</v>
+      </c>
+      <c r="J12" s="6">
+        <v>45231</v>
+      </c>
+      <c r="K12" s="6">
+        <v>45231</v>
+      </c>
+      <c r="L12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="6">
+        <f t="shared" si="0"/>
+        <v>45099</v>
+      </c>
+      <c r="N12" s="6">
+        <v>45099</v>
+      </c>
+      <c r="O12" s="6">
+        <f t="shared" si="2"/>
+        <v>45231</v>
+      </c>
+      <c r="P12" s="6">
+        <f>E12</f>
+        <v>45291</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699C8987-A710-46C3-AE0B-440327ADA1F6}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/reference_files/2023_deployment_dates.xlsx
+++ b/reference_files/2023_deployment_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Senior Year - College\Research\CalibrationCodes\Torrias2025Calibration\voz-data-analysis\reference_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC977ED-A4C3-4A14-9625-ABD61D8BC5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D42F6E-1D14-4467-A41C-822DF09B4153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6397,8 +6397,8 @@
         <v>45231</v>
       </c>
       <c r="P2" s="6">
-        <f>E2</f>
-        <v>45291</v>
+        <f>E2+1</f>
+        <v>45292</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -6455,7 +6455,8 @@
         <v>45239</v>
       </c>
       <c r="P3" s="6">
-        <v>45249</v>
+        <f t="shared" ref="P3:P12" si="2">E3+1</f>
+        <v>45270</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -6513,8 +6514,8 @@
         <v>45238</v>
       </c>
       <c r="P4" s="6">
-        <f>DatesAvailable!C146</f>
-        <v>45269</v>
+        <f t="shared" si="2"/>
+        <v>45280</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -6570,6 +6571,7 @@
         <v>45244</v>
       </c>
       <c r="P5" s="6">
+        <f t="shared" si="2"/>
         <v>45292</v>
       </c>
     </row>
@@ -6626,6 +6628,7 @@
         <v>45247</v>
       </c>
       <c r="P6" s="6">
+        <f t="shared" si="2"/>
         <v>45292</v>
       </c>
     </row>
@@ -6682,6 +6685,7 @@
         <v>45247</v>
       </c>
       <c r="P7" s="6">
+        <f t="shared" si="2"/>
         <v>45281</v>
       </c>
     </row>
@@ -6738,6 +6742,7 @@
         <v>45238</v>
       </c>
       <c r="P8" s="6">
+        <f t="shared" si="2"/>
         <v>45280</v>
       </c>
     </row>
@@ -6794,6 +6799,7 @@
         <v>45246</v>
       </c>
       <c r="P9" s="6">
+        <f t="shared" si="2"/>
         <v>45270</v>
       </c>
     </row>
@@ -6850,6 +6856,7 @@
         <v>45238</v>
       </c>
       <c r="P10" s="6">
+        <f t="shared" si="2"/>
         <v>45292</v>
       </c>
     </row>
@@ -6906,6 +6913,7 @@
         <v>45248</v>
       </c>
       <c r="P11" s="6">
+        <f t="shared" si="2"/>
         <v>45280</v>
       </c>
     </row>
@@ -6960,8 +6968,8 @@
         <v>45231</v>
       </c>
       <c r="P12" s="6">
-        <f>E12</f>
-        <v>45291</v>
+        <f t="shared" si="2"/>
+        <v>45292</v>
       </c>
     </row>
   </sheetData>

--- a/reference_files/2023_deployment_dates.xlsx
+++ b/reference_files/2023_deployment_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Senior Year - College\Research\CalibrationCodes\Torrias2025Calibration\voz-data-analysis\reference_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D42F6E-1D14-4467-A41C-822DF09B4153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217985C0-ADF9-4F86-A0DC-2A30F34332AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6447,7 +6447,7 @@
         <v>45092</v>
       </c>
       <c r="N3" s="6">
-        <f t="shared" ref="N3:N12" ca="1" si="0">H3</f>
+        <f t="shared" ref="N3:N11" ca="1" si="0">H3</f>
         <v>45104</v>
       </c>
       <c r="O3" s="6">
@@ -7148,7 +7148,7 @@
         <v>45092</v>
       </c>
       <c r="N3" s="6">
-        <f t="shared" ref="N3:N12" ca="1" si="0">H3</f>
+        <f t="shared" ref="N3:N11" ca="1" si="0">H3</f>
         <v>45104</v>
       </c>
       <c r="O3" s="6">
@@ -7850,7 +7850,7 @@
         <v>45104</v>
       </c>
       <c r="N3" s="6">
-        <f t="shared" ref="N3:N12" ca="1" si="1">H3</f>
+        <f t="shared" ref="N3:N11" ca="1" si="1">H3</f>
         <v>45104</v>
       </c>
       <c r="O3" s="6">
